--- a/dev/trails/stock_asset_grouped_temporal_defaults.xlsx
+++ b/dev/trails/stock_asset_grouped_temporal_defaults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\premise_trails\dev\trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DDCD3C-FB8A-4CB8-85D1-936911740A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCA5EDC-7DDD-44BC-AE5D-E3A380319DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="-21600" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="335">
   <si>
     <t>Stock asset grouped temporal defaults</t>
   </si>
@@ -1024,6 +1024,24 @@
   </si>
   <si>
     <t xml:space="preserve">2: lognormal | Uses loc as median lag before commissioning (negative years) and scale as geometric spread factor (GSD). </t>
+  </si>
+  <si>
+    <t>slanted-roof construction, mounted, on roof</t>
+  </si>
+  <si>
+    <t>open ground construction, on ground</t>
+  </si>
+  <si>
+    <t>open ground construction</t>
+  </si>
+  <si>
+    <t>building construction, luxury hotel</t>
+  </si>
+  <si>
+    <t>hotel</t>
+  </si>
+  <si>
+    <t>building, luxury hotel</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1051,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,6 +1102,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1130,7 +1154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1174,6 +1198,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1539,8 +1564,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="KeywordMappingTable" displayName="KeywordMappingTable" ref="A1:D57">
-  <autoFilter ref="A1:D57" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="KeywordMappingTable" displayName="KeywordMappingTable" ref="A1:D62">
+  <autoFilter ref="A1:D62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="keyword"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="group"/>
@@ -2157,7 +2182,7 @@
         <v>61</v>
       </c>
       <c r="B7" s="6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
@@ -2166,11 +2191,11 @@
         <v>35</v>
       </c>
       <c r="E7" s="7">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="7">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="H7" s="7">
         <v>-1</v>
@@ -2940,10 +2965,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="30.41796875" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
@@ -3021,958 +3046,973 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
-        <v>161</v>
+        <v>332</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2" t="s">
-        <v>163</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A7" s="15" t="s">
+        <v>334</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>164</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
-        <v>165</v>
+        <v>333</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>166</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2">
         <v>90</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C15" s="2">
         <v>100</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C23" s="2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>100</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C31" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C33" s="2">
         <v>100</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C34" s="2">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>100</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C38" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C40" s="2">
         <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C41" s="2">
         <v>95</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C42" s="2">
         <v>90</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="2" t="s">
-        <v>225</v>
+      <c r="A43" t="s">
+        <v>330</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="2">
+        <v>90</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="2">
+        <v>90</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="2">
-        <v>85</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="2">
+        <v>100</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C44" s="2">
-        <v>85</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="2">
-        <v>90</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="C46" s="2">
         <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="2">
+        <v>90</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="2">
+        <v>85</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="2">
+        <v>85</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="2">
-        <v>95</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="C50" s="2">
+        <v>90</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C48" s="2">
-        <v>95</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="2">
-        <v>100</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="2">
-        <v>95</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C51" s="2">
         <v>95</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2">
         <v>95</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C54" s="2">
         <v>100</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C55" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C56" s="2">
         <v>95</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="2">
+        <v>95</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="2">
+        <v>100</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="2">
+        <v>100</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="2">
+        <v>100</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="2">
+        <v>95</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C62" s="2">
         <v>100</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>249</v>
-      </c>
-      <c r="B58" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58">
-        <v>100</v>
-      </c>
-      <c r="D58" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>250</v>
-      </c>
-      <c r="B59" t="s">
-        <v>113</v>
-      </c>
-      <c r="C59">
-        <v>95</v>
-      </c>
-      <c r="D59" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>251</v>
-      </c>
-      <c r="B60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60">
-        <v>95</v>
-      </c>
-      <c r="D60" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>252</v>
-      </c>
-      <c r="B61" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61">
-        <v>100</v>
-      </c>
-      <c r="D61" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>253</v>
-      </c>
-      <c r="B62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62">
-        <v>95</v>
-      </c>
-      <c r="D62" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C63">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C64">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C65">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C66">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D66" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C67">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
-        <v>125</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C68">
         <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C69">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D69" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C70">
         <v>100</v>
       </c>
+      <c r="D70" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C71">
-        <v>85</v>
+        <v>90</v>
+      </c>
+      <c r="D71" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>263</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C72">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="D72" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C73">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="D73" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C74">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="D74" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B75" t="s">
         <v>130</v>
@@ -3983,54 +4023,54 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B76" t="s">
         <v>130</v>
       </c>
       <c r="C76">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B77" t="s">
         <v>130</v>
       </c>
       <c r="C77">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B78" t="s">
         <v>130</v>
       </c>
       <c r="C78">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B79" t="s">
         <v>130</v>
       </c>
       <c r="C79">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C80">
         <v>100</v>
@@ -4038,87 +4078,87 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C81">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C82">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C83">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B84" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C84">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C85">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="B86" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C86">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B87" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C87">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B88" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C88">
         <v>100</v>
@@ -4126,78 +4166,133 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B89" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C89">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C90">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C91">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C92">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C93">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B94" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C94">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B95" t="s">
         <v>144</v>
       </c>
       <c r="C95">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>280</v>
+      </c>
+      <c r="B96" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>281</v>
+      </c>
+      <c r="B97" t="s">
+        <v>144</v>
+      </c>
+      <c r="C97">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>282</v>
+      </c>
+      <c r="B98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C98">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" t="s">
+        <v>144</v>
+      </c>
+      <c r="C99">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>284</v>
+      </c>
+      <c r="B100" t="s">
+        <v>144</v>
+      </c>
+      <c r="C100">
         <v>85</v>
       </c>
     </row>
